--- a/docs/角色權限矩陣.xlsx
+++ b/docs/角色權限矩陣.xlsx
@@ -566,7 +566,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>dashboard、projects、tracking、mywork、affairs、finance、stats、settings</t>
+          <t>dashboard、projects、tracking、mywork、affairs、finance、payroll、stats、settings</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -598,12 +598,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>dashboard、projects、tracking、mywork、affairs、finance、stats、settings</t>
+          <t>dashboard、projects、tracking、mywork、affairs、finance、payroll、stats、settings</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>老闆／經理。什麼頁面都看得到、什麼都能改，含公司現有現金與產能統計</t>
+          <t>老闆／經理。什麼頁面都看得到、什麼都能改，含公司現有現金、產能統計與薪資</t>
         </is>
       </c>
     </row>
@@ -630,12 +630,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>dashboard、projects、tracking、mywork、affairs、finance、stats、settings</t>
+          <t>dashboard、projects、tracking、mywork、affairs、finance、payroll、stats、settings</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>會計。什麼頁面都看得到，但只能改金流（應收、應付、登錄付款）與自己的任務</t>
+          <t>會計。什麼頁面都看得到，但只能改金流（應收、應付、登錄付款）、算薪水（D57）與自己的任務</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1425,12 +1425,12 @@
     <row r="19" ht="32" customHeight="1">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>統計</t>
+          <t>薪資</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>產能與工數（員工做了多少）</t>
+          <t>月薪資（每個人領多少、每一行怎麼算出來的）</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1443,9 +1443,9 @@
           <t>✔ 可用</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
-        <is>
-          <t>✘ 看不到</t>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
         </is>
       </c>
       <c r="F19" s="8" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>涉及員工表現評比，只有經理</t>
+          <t>★ 比金流更嚴：金流是公司對外的錢，薪資是同事領多少——所以另立一個權限碼，不跟 view_money 共用</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>金額類統計（單價走勢、流程花費）</t>
+          <t>員工薪資設定（時薪、投保級距、眷屬口數）</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1499,14 +1499,10 @@
       <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21" ht="32" customHeight="1">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>設定</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>客戶、廠商、員工名冊（查電話與聯絡人）</t>
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>法規參數（最低工資、加班倍率、勞健保費率）</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1524,27 +1520,31 @@
           <t>✔ 可用</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>✔ 可用</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>✔ 可用</t>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>頁面所有人都看得到，新增／修改的按鈕才跟權限走</t>
+          <t>每年修法都會動，所以做成可編輯欄位而不是程式常數</t>
         </is>
       </c>
     </row>
     <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="2" t="inlineStr"/>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>維護客戶／廠商／員工、重設密碼</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>統計</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>產能與工數（員工做了多少）</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1557,130 +1557,244 @@
           <t>✔ 可用</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>👁 只能看</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>👁 只能看</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>👁 只能看</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr"/>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>涉及員工表現評比，只有經理</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="32" customHeight="1">
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
+          <t>金額類統計（單價走勢、流程花費）</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="32" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>設定</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>客戶、廠商、員工名冊（查電話與聯絡人）</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>頁面所有人都看得到，新增／修改的按鈕才跟權限走</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>維護客戶／廠商／員工、重設密碼</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>👁 只能看</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>👁 只能看</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>👁 只能看</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>流程模板（新案的預設流程；可拖曳排序）</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>✔ 可用</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>✔ 可用</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>✘ 看不到</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>✘ 看不到</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>✘ 看不到</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>這兩個子分頁本身就只有能維護主檔的人看得到，其他角色連分頁都沒有</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="2" t="inlineStr"/>
-      <c r="B24" s="2" t="inlineStr">
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>構件批次站別（幾站、叫什麼、顏色；可拖曳排序）</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>✔ 可用</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>✔ 可用</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>✘ 看不到</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>✘ 看不到</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>✘ 看不到</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>✔ 可用</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>✘ 看不到</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>D54 起搬到網站上；Django Admin 已移除</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>圖例</t>
         </is>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>✔ 可用＝可以看也可以改／可以用　　👁 只能看＝看得到但改不了　　✘ 看不到＝連分頁都不會出現</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
         <is>
           <t>用不到的分頁是**不顯示**，不是變灰——看到自己用不到的東西只是負荷。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr">
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
         <is>
           <t>員工對「指派給自己的」單元與行政事項，不論角色都能回報進度與勾完成（那是資料層的關係，不在這張表裡）。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
         <is>
           <t>所有金額欄位另外由「看得到金額」把關：員工與檢視在任何頁面拿到的金額都是空的。</t>
         </is>
@@ -1697,7 +1811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2375,77 +2489,127 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>view_payroll</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>看薪資分頁（每位同事的薪水）</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>✘</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>✘</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>edit_payroll</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>算薪水、改薪資設定與法規參數</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>✔</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>✘</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>✘</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>這一頁由 main/utils/permissions.py 直接算出來——程式改了，重跑這支腳本就同步。</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>分頁</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>需要的權限（任一即可，空白＝所有登入者）</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>dashboard</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>view_overview</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>projects</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>view_overview</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>tracking</t>
+          <t>dashboard</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>（所有登入者）</t>
+          <t>view_overview</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mywork</t>
+          <t>projects</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>view_mywork</t>
+          <t>view_overview</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>affairs</t>
+          <t>tracking</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2457,34 +2621,70 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>finance</t>
+          <t>mywork</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>view_money</t>
+          <t>view_mywork</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>stats</t>
+          <t>affairs</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>view_productivity、view_money</t>
+          <t>（所有登入者）</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>finance</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>view_money</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>payroll</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>view_payroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>stats</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>view_productivity、view_money</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>settings</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>（所有登入者）</t>
         </is>
